--- a/output/topology_excel/12611.xlsx
+++ b/output/topology_excel/12611.xlsx
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>167</v>
+        <v>95</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>90</v>
+        <v>410</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,15 +718,15 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>143</v>
+        <v>262</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="n">
         <v>7</v>
@@ -740,18 +740,18 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>133</v>
+        <v>414</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,15 +762,15 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>278</v>
+        <v>167</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
         <v>6</v>
@@ -784,18 +784,18 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>262</v>
+        <v>143</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -817,7 +817,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,15 +828,15 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" t="n">
         <v>5</v>
@@ -850,10 +850,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>147</v>
+        <v>278</v>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>174</v>
+        <v>90</v>
       </c>
       <c r="F22" t="n">
         <v>11</v>
@@ -924,7 +924,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" t="n">
         <v>7</v>
@@ -938,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>101</v>
+        <v>193</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
@@ -949,7 +949,7 @@
         <v>6</v>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>414</v>
+        <v>147</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -971,7 +971,7 @@
         <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,19 +982,19 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" t="n">
         <v>8</v>
       </c>
-      <c r="B26" t="n">
-        <v>9</v>
-      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>410</v>
+        <v>101</v>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/12611.xlsx
+++ b/output/topology_excel/12611.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>19</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>11</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>11</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>11</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>12</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>11</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>12</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>12</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>12</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>12</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>12</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>12</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>12</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>30</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>11</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -803,13 +843,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F17" t="n">
-        <v>49</v>
+        <v>11</v>
+      </c>
+      <c r="G17" t="n">
+        <v>38</v>
+      </c>
+      <c r="H17" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -833,6 +879,8 @@
       <c r="F18" t="n">
         <v>11</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +903,8 @@
       <c r="F19" t="n">
         <v>12</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +927,8 @@
       <c r="F20" t="n">
         <v>12</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +951,8 @@
       <c r="F21" t="n">
         <v>19</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +975,8 @@
       <c r="F22" t="n">
         <v>11</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +999,8 @@
       <c r="F23" t="n">
         <v>11</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1023,8 @@
       <c r="F24" t="n">
         <v>21</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1047,8 @@
       <c r="F25" t="n">
         <v>11</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1071,8 @@
       <c r="F26" t="n">
         <v>11</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
